--- a/stories/arbres/TREE-AUT-002.xlsx
+++ b/stories/arbres/TREE-AUT-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est près de la fenêtre, avec papa. Maman ouvre un peu le store. Dehors, l'air est frais. Nora va sortir. Papa dit : prendre son manteau. Puis on sort. Quand on rentre, on raccroche le manteau.</t>
+          <t>Nora est près de la fenêtre, avec papa. Maman ouvre un peu le store. Dehors, l'air est frais. Nora va sortir. Prendre son manteau. Puis on sort. Quand on rentre, on raccroche le manteau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est près de la fenêtre, avec papa. Maman ouvre un peu le store. Dehors, l'air est frais. Nora va sortir.
+papa|Prendre son manteau.
+narrateur|Puis on sort. Quand on rentre, on raccroche le manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1544,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora prend son manteau rouge. Elle le ferme. Elle sort. Le vent est doux. Puis elle rentre. Elle raccroche le manteau. Papa dit : tu as pris ton manteau. Maman sourit.</t>
+          <t>Nora prend son manteau rouge. Elle le ferme. Elle sort. Le vent est doux. Puis elle rentre. Elle raccroche le manteau. Tu as pris ton manteau. Maman sourit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1682,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend son manteau rouge. Elle le ferme. Elle sort. Le vent est doux. Puis elle rentre. Elle raccroche le manteau.
+papa|Tu as pris ton manteau. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1868,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Avant de sortir, on prend son manteau ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2041,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On prend son manteau avant de sortir. Nora respire. Papa est là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2236,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2403,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le ballon rouge. Elle a pris son manteau. Elle joue. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2543,6 +2598,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2705,6 +2765,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi rouge. Puis le ballon rouge. Puis le chat. Un ballon s'immobilise. Nora range encore un peu, près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2932,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3099,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. Une cloche tinte, tout loin. Nora souffle, puis sourit à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3266,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3433,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nora se souvient de rouge. Et de le ballon rouge. Et de la poule. L'eau coule, tout petit bruit. Nora marche près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3600,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3539,7 +3629,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le seau bleu. Elle a pris son manteau. Elle puise des feuilles. Puis elle rentre. Elle raccroche le manteau. Papa dit : je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Nora sort avec le seau bleu. Elle a pris son manteau. Elle puise des feuilles. Puis elle rentre. Elle raccroche le manteau. Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3677,6 +3767,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le seau bleu. Elle a pris son manteau. Elle puise des feuilles. Puis elle rentre. Elle raccroche le manteau.
+papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3867,6 +3963,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4029,6 +4130,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après le seau bleu. Près de rouge. Nora s'arrête. On se tient la main. Nora range rouge dans sa tête, comme un souvenir. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4297,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4353,6 +4464,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nora range le seau bleu. le chien reste près de rouge. Une chaussette est encore sablée. Nora pose sa tête un moment. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4631,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4539,7 +4660,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. le seau bleu aussi. rouge reste dans le souvenir. On rit un peu. Nora enfile ses chaussons. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule est là. le seau bleu aussi. rouge reste dans le souvenir. On rit un peu. Nora enfile ses chaussons. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4677,6 +4798,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. le seau bleu aussi. rouge reste dans le souvenir. On rit un peu. Nora enfile ses chaussons. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4965,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5132,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le doudou. Elle a pris son manteau. Elle tient le doudou. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5191,6 +5327,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5353,6 +5494,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint le chat. le doudou est rangé. rouge est fini. Un ruban reste dans la poche. Nora prend la main de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5661,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5677,6 +5828,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Nora pose le doudou. rouge est derrière. Ça sent le pain chaud. Nora ferme le sac. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5995,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6001,6 +6162,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poule. Papa a vu rouge. Et le doudou. On attend son tour. Nora chuchote : c'est fini. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6329,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6187,7 +6358,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nora prend son manteau bleu. Elle le boutonne. Elle sort. La lumière est claire. Puis elle rentre. Elle raccroche le manteau. Papa dit : le manteau a sa place.</t>
+          <t>Nora prend son manteau bleu. Elle le boutonne. Elle sort. La lumière est claire. Puis elle rentre. Elle raccroche le manteau. Le manteau a sa place.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6325,6 +6496,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend son manteau bleu. Elle le boutonne. Elle sort. La lumière est claire. Puis elle rentre. Elle raccroche le manteau.
+papa|Le manteau a sa place.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6682,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On prend quoi ? Le manteau.</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6855,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On prend son manteau avant de sortir. Nora retient le geste. Papa sourit. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7050,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6887,7 +7079,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le ballon rouge, manteau boutonné. Un chat passe. Elle joue. Puis elle rentre. Elle raccroche le manteau. Papa dit : je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Nora sort avec le ballon rouge, manteau boutonné. Un chat passe. Elle joue. Puis elle rentre. Elle raccroche le manteau. Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7025,6 +7217,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le ballon rouge, manteau boutonné. Un chat passe. Elle joue. Puis elle rentre. Elle raccroche le manteau.
+papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7215,6 +7413,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7377,6 +7580,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi bleu. Puis le ballon rouge. Puis le chat. Un vélo passe au loin. Nora sourit. Papa sourit aussi. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7747,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7914,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. Un linge sèche à l'air. Nora s'assoit près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8081,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8248,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nora se souvient de bleu. Et de le ballon rouge. Et de la poule. On entend un oiseau. Nora écoute papa encore une fois. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8415,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8582,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le seau bleu, manteau boutonné. Un chat miaule. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8539,6 +8777,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8563,7 +8806,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après le seau bleu. Près de bleu. Nora s'arrête. Un chat miaule une fois. Nora dit : j'ai appris. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Avec le chat. Après le seau bleu. Près de bleu. Nora s'arrête. Un chat miaule une fois. J'ai appris. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8701,6 +8944,13 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après le seau bleu. Près de bleu. Nora s'arrête. Un chat miaule une fois.
+enfant-f|J'ai appris. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau.
+narrateur|Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9113,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9280,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nora range le seau bleu. le chien reste près de bleu. Le sol est un peu froid. Nora ferme la porte, tout doux. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9447,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9211,7 +9476,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. le seau bleu aussi. bleu reste dans le souvenir. La lumière est claire. Nora raccroche un linge. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule est là. le seau bleu aussi. bleu reste dans le souvenir. La lumière est claire. Nora raccroche un linge. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9349,6 +9614,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. le seau bleu aussi. bleu reste dans le souvenir. La lumière est claire. Nora raccroche un linge. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9781,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9948,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le doudou, manteau boutonné. Un chat se frotte. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9863,6 +10143,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10025,6 +10310,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint le chat. le doudou est rangé. bleu est fini. On écoute jusqu'au bout. Nora range la tasse. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10477,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10644,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Nora pose le doudou. bleu est derrière. Le vent est doux. Nora caresse le doudou. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10811,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10978,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poule. Papa a vu bleu. Et le doudou. Les chaussures font toc toc. Nora dit merci à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11145,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10997,6 +11312,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend son manteau vert. Elle enfile les manches. Elle sort. Une feuille colle au tissu. Puis elle rentre. Elle raccroche le manteau. Maman l'aide à trouver le crochet.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11177,6 +11497,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Quand on rentre, on raccroche le manteau ?</t>
         </is>
       </c>
     </row>
@@ -11345,6 +11670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On prend son manteau avant de sortir. Nora hoche la tête. On continue, avec papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11535,6 +11865,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11697,6 +12032,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le ballon. Un chien marche au loin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11887,6 +12227,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12049,6 +12394,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi vert. Puis le ballon rouge. Puis le chat. Une pomme brille un peu. Nora boit une gorgée d'eau. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12211,6 +12561,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12373,6 +12728,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. On dit merci. Maman n'est pas loin. Nora les rejoint. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12535,6 +12895,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12697,6 +13062,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nora se souvient de vert. Et de le ballon rouge. Et de la poule. Un panier est posé sur le banc. Nora serre la main de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12859,6 +13229,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13021,6 +13396,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le seau. Un chien marche au loin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13211,6 +13591,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13373,6 +13758,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après le seau bleu. Près de vert. Nora s'arrête. Une feuille tombe. Nora plie un pull. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13535,6 +13925,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13697,6 +14092,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nora range le seau bleu. le chien reste près de vert. Le savon sent bon. Nora pose le seau bleu à sa place. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13859,6 +14259,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13883,7 +14288,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. le seau bleu aussi. vert reste dans le souvenir. On range un objet. Nora montre la poule à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule est là. le seau bleu aussi. vert reste dans le souvenir. On range un objet. Nora montre la poule à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14021,6 +14426,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. le seau bleu aussi. vert reste dans le souvenir. On range un objet. Nora montre la poule à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14183,6 +14593,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14207,7 +14622,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le doudou. Une poule caquette chez le voisin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa dit : je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Nora sort avec le doudou. Une poule caquette chez le voisin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14345,6 +14760,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nora sort avec le doudou. Une poule caquette chez le voisin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau.
+papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14535,6 +14956,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14697,6 +15123,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint le chat. le doudou est rangé. vert est fini. On souffle doucement. Nora tend le chat à maman. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14859,6 +15290,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15021,6 +15457,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Nora pose le doudou. vert est derrière. Un galet est encore chaud. Nora répète tout bas le geste. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15183,6 +15624,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15345,6 +15791,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poule. Papa a vu vert. Et le doudou. Il y a des miettes sur la table. Nora essuie ses mains. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15507,6 +15958,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15525,7 +15981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15542,6 +15998,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-002.xlsx
+++ b/stories/arbres/TREE-AUT-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Puis on sort. Quand on rentre, on raccroche le manteau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1688,6 +1695,7 @@
 papa|Tu as pris ton manteau. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1875,6 +1883,7 @@
           <t>narrateur|Avant de sortir, on prend son manteau ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2046,6 +2055,7 @@
           <t>narrateur|Oui. On prend son manteau avant de sortir. Nora respire. Papa est là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2241,6 +2251,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2408,6 +2419,7 @@
           <t>narrateur|Nora sort avec le ballon rouge. Elle a pris son manteau. Elle joue. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2601,6 +2613,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2770,6 +2787,7 @@
           <t>narrateur|Nora a choisi rouge. Puis le ballon rouge. Puis le chat. Un ballon s'immobilise. Nora range encore un peu, près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2937,6 +2955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3104,6 +3123,11 @@
           <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. Une cloche tinte, tout loin. Nora souffle, puis sourit à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3271,6 +3295,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3438,6 +3463,7 @@
           <t>narrateur|Nora se souvient de rouge. Et de le ballon rouge. Et de la poule. L'eau coule, tout petit bruit. Nora marche près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3605,6 +3631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3773,6 +3800,7 @@
 papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3966,6 +3994,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4135,6 +4168,7 @@
           <t>narrateur|Avec le chat. Après le seau bleu. Près de rouge. Nora s'arrête. On se tient la main. Nora range rouge dans sa tête, comme un souvenir. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4302,6 +4336,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4469,6 +4504,11 @@
           <t>narrateur|Nora range le seau bleu. le chien reste près de rouge. Une chaussette est encore sablée. Nora pose sa tête un moment. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4636,6 +4676,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4803,6 +4844,7 @@
           <t>narrateur|La poule est là. le seau bleu aussi. rouge reste dans le souvenir. On rit un peu. Nora enfile ses chaussons. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4970,6 +5012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5137,6 +5180,7 @@
           <t>narrateur|Nora sort avec le doudou. Elle a pris son manteau. Elle tient le doudou. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5330,6 +5374,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5499,6 +5548,7 @@
           <t>narrateur|Nora rejoint le chat. le doudou est rangé. rouge est fini. Un ruban reste dans la poche. Nora prend la main de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5666,6 +5716,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5833,6 +5884,11 @@
           <t>narrateur|Près de le chien. Nora pose le doudou. rouge est derrière. Ça sent le pain chaud. Nora ferme le sac. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6000,6 +6056,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6167,6 +6224,7 @@
           <t>narrateur|Nora montre la poule. Papa a vu rouge. Et le doudou. On attend son tour. Nora chuchote : c'est fini. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6334,6 +6392,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6502,6 +6561,7 @@
 papa|Le manteau a sa place.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6689,6 +6749,7 @@
           <t>narrateur|On prend quoi ? Le manteau.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6860,6 +6921,7 @@
           <t>narrateur|Oui. On prend son manteau avant de sortir. Nora retient le geste. Papa sourit. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7055,6 +7117,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7223,6 +7286,7 @@
 papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7416,6 +7480,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7585,6 +7654,7 @@
           <t>narrateur|Nora a choisi bleu. Puis le ballon rouge. Puis le chat. Un vélo passe au loin. Nora sourit. Papa sourit aussi. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7752,6 +7822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7919,6 +7990,11 @@
           <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. Un linge sèche à l'air. Nora s'assoit près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8086,6 +8162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8253,6 +8330,7 @@
           <t>narrateur|Nora se souvient de bleu. Et de le ballon rouge. Et de la poule. On entend un oiseau. Nora écoute papa encore une fois. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8420,6 +8498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8587,6 +8666,7 @@
           <t>narrateur|Nora sort avec le seau bleu, manteau boutonné. Un chat miaule. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8780,6 +8860,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8951,6 +9036,7 @@
 narrateur|Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9118,6 +9204,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9285,6 +9372,11 @@
           <t>narrateur|Nora range le seau bleu. le chien reste près de bleu. Le sol est un peu froid. Nora ferme la porte, tout doux. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9452,6 +9544,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9619,6 +9712,7 @@
           <t>narrateur|La poule est là. le seau bleu aussi. bleu reste dans le souvenir. La lumière est claire. Nora raccroche un linge. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9786,6 +9880,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9953,6 +10048,7 @@
           <t>narrateur|Nora sort avec le doudou, manteau boutonné. Un chat se frotte. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10146,6 +10242,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10315,6 +10416,7 @@
           <t>narrateur|Nora rejoint le chat. le doudou est rangé. bleu est fini. On écoute jusqu'au bout. Nora range la tasse. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10482,6 +10584,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10649,6 +10752,11 @@
           <t>narrateur|Près de le chien. Nora pose le doudou. bleu est derrière. Le vent est doux. Nora caresse le doudou. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10816,6 +10924,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10983,6 +11092,7 @@
           <t>narrateur|Nora montre la poule. Papa a vu bleu. Et le doudou. Les chaussures font toc toc. Nora dit merci à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11150,6 +11260,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11317,6 +11428,7 @@
           <t>narrateur|Nora prend son manteau vert. Elle enfile les manches. Elle sort. Une feuille colle au tissu. Puis elle rentre. Elle raccroche le manteau. Maman l'aide à trouver le crochet.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11504,6 +11616,7 @@
           <t>narrateur|Quand on rentre, on raccroche le manteau ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11675,6 +11788,7 @@
           <t>narrateur|Oui. On prend son manteau avant de sortir. Nora hoche la tête. On continue, avec papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11870,6 +11984,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12037,6 +12152,11 @@
           <t>narrateur|Nora sort avec le ballon. Un chien marche au loin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12230,6 +12350,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12399,6 +12524,7 @@
           <t>narrateur|Nora a choisi vert. Puis le ballon rouge. Puis le chat. Une pomme brille un peu. Nora boit une gorgée d'eau. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12566,6 +12692,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12733,6 +12860,11 @@
           <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. On dit merci. Maman n'est pas loin. Nora les rejoint. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12900,6 +13032,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13067,6 +13200,7 @@
           <t>narrateur|Nora se souvient de vert. Et de le ballon rouge. Et de la poule. Un panier est posé sur le banc. Nora serre la main de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13234,6 +13368,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13401,6 +13536,11 @@
           <t>narrateur|Nora sort avec le seau. Un chien marche au loin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13594,6 +13734,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13763,6 +13908,7 @@
           <t>narrateur|Avec le chat. Après le seau bleu. Près de vert. Nora s'arrête. Une feuille tombe. Nora plie un pull. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13930,6 +14076,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14097,6 +14244,11 @@
           <t>narrateur|Nora range le seau bleu. le chien reste près de vert. Le savon sent bon. Nora pose le seau bleu à sa place. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14264,6 +14416,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14431,6 +14584,7 @@
           <t>narrateur|La poule est là. le seau bleu aussi. vert reste dans le souvenir. On range un objet. Nora montre la poule à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14598,6 +14752,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14766,6 +14921,7 @@
 papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14959,6 +15115,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15128,6 +15289,7 @@
           <t>narrateur|Nora rejoint le chat. le doudou est rangé. vert est fini. On souffle doucement. Nora tend le chat à maman. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15295,6 +15457,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15462,6 +15625,11 @@
           <t>narrateur|Près de le chien. Nora pose le doudou. vert est derrière. Un galet est encore chaud. Nora répète tout bas le geste. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15629,6 +15797,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15796,6 +15965,7 @@
           <t>narrateur|Nora montre la poule. Papa a vu vert. Et le doudou. Il y a des miettes sur la table. Nora essuie ses mains. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15963,6 +16133,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15981,7 +16152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16005,6 +16176,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16019,7 +16204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16206,6 +16391,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-002.xlsx
+++ b/stories/arbres/TREE-AUT-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prendre son manteau avant de sortir — près de la fenêtre</t>
+          <t>Le manteau de Sarah près de la vitre embuée</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut jouer dehors. Elle prend son manteau, sort, rentre, et le raccroche.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est près de la fenêtre, avec papa. Maman ouvre un peu le store. Dehors, l'air est frais. Nora va sortir. Prendre son manteau. Puis on sort. Quand on rentre, on raccroche le manteau.</t>
+          <t>La vitre de l'entrée est toute embuée. Sarah y dessine un petit rond du doigt. Dehors, le jardin est gris et frais. Les feuilles collent au banc de bois. Un crochet de manteau attend près de la porte. Le crochet est bas, à hauteur d'enfant. Ça sent la terre mouillée, tout doux. L'horloge de la cuisine fait tic tac. Papa lace une chaussure, puis l'autre. Les chaussures sont prêtes, Sarah. Maman soulève un peu le store. Tu as vu le banc, tout mouillé ? Oui, maman. Trois manteaux pendent, rouge, bleu, vert. Je veux sortir ! Je veux jouer dehors. D'accord. Avant de sortir, on prend son manteau. Quand on rentre, on le raccroche. Sarah touche le tissu le plus proche. En ce moment, elle a trop envie de courir au jardin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,9 +1337,27 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nora est près de la fenêtre, avec papa. Maman ouvre un peu le store. Dehors, l'air est frais. Nora va sortir.
-papa|Prendre son manteau.
-narrateur|Puis on sort. Quand on rentre, on raccroche le manteau.</t>
+          <t>narrateur|La vitre de l'entrée est toute embuée.
+narrateur|Sarah y dessine un petit rond du doigt.
+narrateur|Dehors, le jardin est gris et frais.
+narrateur|Les feuilles collent au banc de bois.
+narrateur|Un crochet de manteau attend près de la porte.
+narrateur|Le crochet est bas, à hauteur d'enfant.
+narrateur|Ça sent la terre mouillée, tout doux.
+narrateur|L'horloge de la cuisine fait tic tac.
+narrateur|Papa lace une chaussure, puis l'autre.
+papa|Les chaussures sont prêtes, Sarah.
+narrateur|Maman soulève un peu le store.
+maman|Tu as vu le banc, tout mouillé ?
+enfant-f|Oui, maman.
+narrateur|Trois manteaux pendent, rouge, bleu, vert.
+enfant-f|Je veux sortir !
+enfant-f|Je veux jouer dehors.
+papa|D'accord.
+papa|Avant de sortir, on prend son manteau.
+maman|Quand on rentre, on le raccroche.
+narrateur|Sarah touche le tissu le plus proche.
+narrateur|En ce moment, elle a trop envie de courir au jardin.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1355,7 +1385,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On peut prendre le manteau rouge, le manteau bleu, ou le manteau vert.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1523,7 +1553,7 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On peut prendre le manteau rouge, le manteau bleu, ou le manteau vert.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1551,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora prend son manteau rouge. Elle le ferme. Elle sort. Le vent est doux. Puis elle rentre. Elle raccroche le manteau. Tu as pris ton manteau. Maman sourit.</t>
+          <t>Sarah prend le manteau rouge. Le tissu est épais, un peu rêche. La fermeture brille. Glisse un bras, puis l'autre. Sarah enfile les manches. Elle ferme le manteau jusqu'en haut. Bravo. Tu as pris ton manteau avant de sortir. Papa ouvre la porte. L'air frais touche les joues. Sarah sort, puis elle rentre un moment. Le crochet, Sarah. Sarah raccroche le manteau rouge. Tu as raccroché. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1691,8 +1721,21 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nora prend son manteau rouge. Elle le ferme. Elle sort. Le vent est doux. Puis elle rentre. Elle raccroche le manteau.
-papa|Tu as pris ton manteau. Maman sourit.</t>
+          <t>narrateur|Sarah prend le manteau rouge.
+narrateur|Le tissu est épais, un peu rêche.
+narrateur|La fermeture brille.
+maman|Glisse un bras, puis l'autre.
+narrateur|Sarah enfile les manches.
+narrateur|Elle ferme le manteau jusqu'en haut.
+papa|Bravo.
+papa|Tu as pris ton manteau avant de sortir.
+narrateur|Papa ouvre la porte.
+narrateur|L'air frais touche les joues.
+narrateur|Sarah sort, puis elle rentre un moment.
+maman|Le crochet, Sarah.
+narrateur|Sarah raccroche le manteau rouge.
+papa|Tu as raccroché.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1908,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On prend son manteau avant de sortir. Nora respire. Papa est là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Oui. On prend son manteau avant de sortir. Quand on rentre, on le raccroche. Bravo, Sarah. Tu as écouté. Le manteau rouge est à sa place. Je peux ressortir ? Oui. On reprend le manteau, puis on sort. D'accord.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2052,7 +2095,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On prend son manteau avant de sortir. Nora respire. Papa est là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Oui.
+narrateur|On prend son manteau avant de sortir.
+narrateur|Quand on rentre, on le raccroche.
+maman|Bravo, Sarah.
+maman|Tu as écouté.
+papa|Le manteau rouge est à sa place.
+enfant-f|Je peux ressortir ?
+papa|Oui.
+papa|On reprend le manteau, puis on sort.
+enfant-f|D'accord.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2276,7 +2328,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le ballon rouge. Elle a pris son manteau. Elle joue. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau rouge. Elle le ferme. Le ballon rouge, Sarah. Le ballon. Le ballon est un peu lisse, un peu froid. Sarah sort. Le ballon rebondit sur le chemin mouillé. Tu as pris ton manteau. Sarah joue, puis elle rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Le ballon attend près de la porte.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2416,7 +2468,19 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le ballon rouge. Elle a pris son manteau. Elle joue. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau rouge.
+narrateur|Elle le ferme.
+papa|Le ballon rouge, Sarah.
+enfant-f|Le ballon.
+narrateur|Le ballon est un peu lisse, un peu froid.
+narrateur|Sarah sort.
+narrateur|Le ballon rebondit sur le chemin mouillé.
+maman|Tu as pris ton manteau.
+narrateur|Sarah joue, puis elle rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+maman|Bravo.
+maman|Le ballon attend près de la porte.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2444,7 +2508,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2612,7 +2676,7 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2644,7 +2708,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi rouge. Puis le ballon rouge. Puis le chat. Un ballon s'immobilise. Nora range encore un peu, près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat gris s'assoit près du ballon. Il cligne des yeux. Le chat. On le regarde, tout doux. Sarah a encore le manteau rouge. Tu as pris ton manteau pour sortir. Le ballon s'immobilise dans l'herbe. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Le chat reste au jardin.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2784,7 +2848,18 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi rouge. Puis le ballon rouge. Puis le chat. Un ballon s'immobilise. Nora range encore un peu, près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chat gris s'assoit près du ballon.
+narrateur|Il cligne des yeux.
+enfant-f|Le chat.
+maman|On le regarde, tout doux.
+narrateur|Sarah a encore le manteau rouge.
+papa|Tu as pris ton manteau pour sortir.
+narrateur|Le ballon s'immobilise dans l'herbe.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+papa|Bravo.
+papa|Le chat reste au jardin.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2812,7 +2887,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon repose près des chaussures. Bravo, Sarah. Tu as raccroché. Merci. Le crochet tient bien le manteau rouge. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2952,7 +3027,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le ballon repose près des chaussures.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Le crochet tient bien le manteau rouge.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2980,7 +3061,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Nora s'arrête près de le chien. le ballon rouge est rangé. Une cloche tinte, tout loin. Nora souffle, puis sourit à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien du chemin remue la queue. Il reste derrière la barrière. On dit bonjour, de loin. Bonjour. Sarah tient le ballon contre le manteau rouge. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Une cloche tinte, tout loin. Le chien reste au chemin.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3120,7 +3201,18 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. Une cloche tinte, tout loin. Nora souffle, puis sourit à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien du chemin remue la queue.
+narrateur|Il reste derrière la barrière.
+papa|On dit bonjour, de loin.
+enfant-f|Bonjour.
+narrateur|Sarah tient le ballon contre le manteau rouge.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+maman|Bravo.
+narrateur|Une cloche tinte, tout loin.
+papa|Le chien reste au chemin.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3152,7 +3244,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah souffle, puis sourit à papa. Bravo, Sarah. Tu as raccroché. Merci, maman. Le manteau rouge sèche un peu, au crochet. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3292,7 +3384,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah souffle, puis sourit à papa.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci, maman.
+narrateur|Le manteau rouge sèche un peu, au crochet.
+papa|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3320,7 +3418,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Nora se souvient de rouge. Et de le ballon rouge. Et de la poule. L'eau coule, tout petit bruit. Nora marche près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule du voisin picore près du grillage. Elle fait un petit bruit. On la regarde, sans courir. La poule. Le ballon reste sous le bras de Sarah. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. L'eau de la gouttière coule, tout petit bruit. La poule reste chez le voisin.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3460,7 +3558,18 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Nora se souvient de rouge. Et de le ballon rouge. Et de la poule. L'eau coule, tout petit bruit. Nora marche près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|La poule du voisin picore près du grillage.
+narrateur|Elle fait un petit bruit.
+maman|On la regarde, sans courir.
+enfant-f|La poule.
+narrateur|Le ballon reste sous le bras de Sarah.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+papa|Bravo.
+narrateur|L'eau de la gouttière coule, tout petit bruit.
+maman|La poule reste chez le voisin.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3488,7 +3597,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah marche près de papa, dans l'entrée. Bravo, Sarah. Tu as fait du bon travail. Merci. Le manteau rouge est à sa place. Avant de sortir, on prend son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3628,7 +3737,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah marche près de papa, dans l'entrée.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le manteau rouge est à sa place.
+maman|Avant de sortir, on prend son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3656,7 +3771,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le seau bleu. Elle a pris son manteau. Elle puise des feuilles. Puis elle rentre. Elle raccroche le manteau. Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau rouge. Elle glisse les manches. Le seau bleu, Sarah. Le seau. Le seau est léger, la anse est lisse. Sarah sort. Elle ramasse des feuilles mouillées. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Le seau reste près des chaussures.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3796,8 +3911,19 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le seau bleu. Elle a pris son manteau. Elle puise des feuilles. Puis elle rentre. Elle raccroche le manteau.
-papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau rouge.
+narrateur|Elle glisse les manches.
+maman|Le seau bleu, Sarah.
+enfant-f|Le seau.
+narrateur|Le seau est léger, la anse est lisse.
+narrateur|Sarah sort.
+narrateur|Elle ramasse des feuilles mouillées.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+papa|Bravo.
+papa|Le seau reste près des chaussures.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3825,7 +3951,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3993,7 +4119,7 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -4025,7 +4151,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après le seau bleu. Près de rouge. Nora s'arrête. On se tient la main. Nora range rouge dans sa tête, comme un souvenir. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat saute sur le banc mouillé. Sarah s'arrête, le seau à la main. On se tient la main. Sarah prend la main de papa. Tu as pris ton manteau. Les feuilles dans le seau sentent l'herbe. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Le seau, je le pose. Oui, près des chaussures.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4165,7 +4291,18 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après le seau bleu. Près de rouge. Nora s'arrête. On se tient la main. Nora range rouge dans sa tête, comme un souvenir. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chat saute sur le banc mouillé.
+narrateur|Sarah s'arrête, le seau à la main.
+papa|On se tient la main.
+narrateur|Sarah prend la main de papa.
+maman|Tu as pris ton manteau.
+narrateur|Les feuilles dans le seau sentent l'herbe.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+maman|Bravo.
+enfant-f|Le seau, je le pose.
+papa|Oui, près des chaussures.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4193,7 +4330,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah range le rouge dans sa tête, comme un souvenir. Bravo, Sarah. Tu as raccroché. Merci, papa. Le seau bleu reste près de la porte. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4333,7 +4470,13 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah range le rouge dans sa tête, comme un souvenir.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci, papa.
+narrateur|Le seau bleu reste près de la porte.
+maman|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4361,7 +4504,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nora range le seau bleu. le chien reste près de rouge. Une chaussette est encore sablée. Nora pose sa tête un moment. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien s'assoit près de la barrière. Une chaussette de Sarah est encore sablée. On dit bonjour, de loin. Bonjour, le chien. Sarah pose le seau un instant. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Sarah pose sa tête un moment contre papa. Le chien reste dehors.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4501,7 +4644,18 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Nora range le seau bleu. le chien reste près de rouge. Une chaussette est encore sablée. Nora pose sa tête un moment. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien s'assoit près de la barrière.
+narrateur|Une chaussette de Sarah est encore sablée.
+maman|On dit bonjour, de loin.
+enfant-f|Bonjour, le chien.
+narrateur|Sarah pose le seau un instant.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+papa|Bravo.
+narrateur|Sarah pose sa tête un moment contre papa.
+maman|Le chien reste dehors.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4533,7 +4687,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah enlève la chaussette sablée, puis la remet. Bravo, Sarah. Tu as raccroché. Merci. Le manteau rouge pend, droit. On a bien sorti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4673,7 +4827,13 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah enlève la chaussette sablée, puis la remet.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Le manteau rouge pend, droit.
+papa|On a bien sorti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4701,7 +4861,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. le seau bleu aussi. rouge reste dans le souvenir. On rit un peu. Nora enfile ses chaussons. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule picore une feuille tombée. Sarah rit un peu, tout bas. On la laisse picorer. Elle a une feuille. Sarah tient le seau bleu. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Sarah enfile ses chaussons. Les chaussons, c'est pour dedans.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4841,7 +5001,18 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. le seau bleu aussi. rouge reste dans le souvenir. On rit un peu. Nora enfile ses chaussons. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|La poule picore une feuille tombée.
+narrateur|Sarah rit un peu, tout bas.
+papa|On la laisse picorer.
+enfant-f|Elle a une feuille.
+narrateur|Sarah tient le seau bleu.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+maman|Bravo.
+narrateur|Sarah enfile ses chaussons.
+papa|Les chaussons, c'est pour dedans.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4869,7 +5040,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le seau bleu reste près du paillasson. Bravo, Sarah. Tu as fait du bon travail. Merci, maman. Le manteau rouge est au crochet. Avant de sortir, on prend son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5009,7 +5180,13 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le seau bleu reste près du paillasson.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le manteau rouge est au crochet.
+maman|Avant de sortir, on prend son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5037,7 +5214,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le doudou. Elle a pris son manteau. Elle tient le doudou. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau rouge. Elle ferme jusqu'en haut. Le doudou, Sarah. Le doudou. Le doudou est chaud contre la manche. Sarah sort. Elle tient le doudou, près du banc mouillé. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Le doudou reste dans ses mains.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5177,7 +5354,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le doudou. Elle a pris son manteau. Elle tient le doudou. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau rouge.
+narrateur|Elle ferme jusqu'en haut.
+papa|Le doudou, Sarah.
+enfant-f|Le doudou.
+narrateur|Le doudou est chaud contre la manche.
+narrateur|Sarah sort.
+narrateur|Elle tient le doudou, près du banc mouillé.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+maman|Bravo.
+maman|Le doudou reste dans ses mains.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5205,7 +5394,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5373,7 +5562,7 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -5405,7 +5594,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint le chat. le doudou est rangé. rouge est fini. Un ruban reste dans la poche. Nora prend la main de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat se frotte contre le doudou. Un ruban dépasse de la poche du manteau. On caresse du bout des doigts. Il est doux. Sarah a encore le manteau rouge. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Le ruban reste dans la poche. Le doudou reste avec toi.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5545,7 +5734,18 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint le chat. le doudou est rangé. rouge est fini. Un ruban reste dans la poche. Nora prend la main de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chat se frotte contre le doudou.
+narrateur|Un ruban dépasse de la poche du manteau.
+maman|On caresse du bout des doigts.
+enfant-f|Il est doux.
+narrateur|Sarah a encore le manteau rouge.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+papa|Bravo.
+narrateur|Le ruban reste dans la poche.
+maman|Le doudou reste avec toi.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5573,7 +5773,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah range le doudou sur la chaise. Bravo, Sarah. Tu as raccroché. Merci. Le manteau rouge attend au crochet. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5713,7 +5913,13 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah range le doudou sur la chaise.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Le manteau rouge attend au crochet.
+papa|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5741,7 +5947,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Nora pose le doudou. rouge est derrière. Ça sent le pain chaud. Nora ferme le sac. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien respire près de la barrière. Ça sent le pain chaud, chez le voisin. On reste de ce côté. Le doudou a vu le chien. Sarah tient le doudou contre le manteau rouge. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Sarah ferme la porte tout doux. Merci.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5881,7 +6087,18 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Nora pose le doudou. rouge est derrière. Ça sent le pain chaud. Nora ferme le sac. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien respire près de la barrière.
+narrateur|Ça sent le pain chaud, chez le voisin.
+papa|On reste de ce côté.
+enfant-f|Le doudou a vu le chien.
+narrateur|Sarah tient le doudou contre le manteau rouge.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+maman|Bravo.
+narrateur|Sarah ferme la porte tout doux.
+papa|Merci.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -5913,7 +6130,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le doudou s'assoit sur la marche de l'entrée. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau rouge n'a plus froid. On a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6053,7 +6270,13 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le doudou s'assoit sur la marche de l'entrée.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci, papa.
+narrateur|Le manteau rouge n'a plus froid.
+maman|On a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6081,7 +6304,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Nora montre la poule. Papa a vu rouge. Et le doudou. On attend son tour. Nora chuchote : c'est fini. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule gonfle ses plumes. Sarah montre la poule du doigt. Tu as vu la poule. Et tu as le doudou. On attend un peu, sans courir. Sarah a encore le manteau rouge. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. C'était la poule. Oui.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6221,7 +6444,18 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Nora montre la poule. Papa a vu rouge. Et le doudou. On attend son tour. Nora chuchote : c'est fini. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|La poule gonfle ses plumes.
+narrateur|Sarah montre la poule du doigt.
+papa|Tu as vu la poule.
+papa|Et tu as le doudou.
+maman|On attend un peu, sans courir.
+narrateur|Sarah a encore le manteau rouge.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau rouge.
+papa|Bravo.
+enfant-f|C'était la poule.
+maman|Oui.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6249,7 +6483,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah chuchote merci à papa. Bravo, Sarah. Tu as fait du bon travail. Le manteau est au crochet. Le doudou reste sur les genoux. Avant de sortir, on prend son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6389,7 +6623,13 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah chuchote merci à papa.
+papa|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+enfant-f|Le manteau est au crochet.
+narrateur|Le doudou reste sur les genoux.
+papa|Avant de sortir, on prend son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6417,7 +6657,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nora prend son manteau bleu. Elle le boutonne. Elle sort. La lumière est claire. Puis elle rentre. Elle raccroche le manteau. Le manteau a sa place.</t>
+          <t>Sarah prend le manteau bleu. Les boutons sont gros et ronds. Elle boutonne le premier, puis le deuxième. Encore un. Sarah boutonne le troisième. Bravo. Tu as pris ton manteau avant de sortir. La lumière de l'entrée est claire. Sarah sort. Le vent bleu touche le tissu. Puis elle rentre. Le crochet, Sarah. Sarah raccroche le manteau bleu. Tu as raccroché. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6557,8 +6797,21 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Nora prend son manteau bleu. Elle le boutonne. Elle sort. La lumière est claire. Puis elle rentre. Elle raccroche le manteau.
-papa|Le manteau a sa place.</t>
+          <t>narrateur|Sarah prend le manteau bleu.
+narrateur|Les boutons sont gros et ronds.
+narrateur|Elle boutonne le premier, puis le deuxième.
+papa|Encore un.
+narrateur|Sarah boutonne le troisième.
+maman|Bravo.
+maman|Tu as pris ton manteau avant de sortir.
+narrateur|La lumière de l'entrée est claire.
+narrateur|Sarah sort.
+narrateur|Le vent bleu touche le tissu.
+narrateur|Puis elle rentre.
+papa|Le crochet, Sarah.
+narrateur|Sarah raccroche le manteau bleu.
+maman|Tu as raccroché.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6586,7 +6839,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On prend quoi ? Le manteau.</t>
+          <t>On prend quoi, avant de sortir ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6746,7 +6999,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|On prend quoi ? Le manteau.</t>
+          <t>narrateur|On prend quoi, avant de sortir ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6774,7 +7027,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On prend son manteau avant de sortir. Nora retient le geste. Papa sourit. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Oui. On prend son manteau. Avant de sortir, on prend son manteau. Bravo, Sarah. Tu as boutonné jusqu'en haut. Quand on rentre, on raccroche le manteau. Il est au crochet. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6918,7 +7171,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On prend son manteau avant de sortir. Nora retient le geste. Papa sourit. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Oui.
+narrateur|On prend son manteau.
+narrateur|Avant de sortir, on prend son manteau.
+papa|Bravo, Sarah.
+papa|Tu as boutonné jusqu'en haut.
+maman|Quand on rentre, on raccroche le manteau.
+enfant-f|Il est au crochet.
+papa|On continue ensemble ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -7142,7 +7403,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le ballon rouge, manteau boutonné. Un chat passe. Elle joue. Puis elle rentre. Elle raccroche le manteau. Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau bleu. Elle boutonne jusqu'en haut. Le ballon rouge, Sarah. Le ballon. Un chat passe près du pas de porte. Sarah sort, manteau boutonné. Le ballon roule vers le banc. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Les boutons sont encore fermés, puis elle les ouvre.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7282,8 +7543,19 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le ballon rouge, manteau boutonné. Un chat passe. Elle joue. Puis elle rentre. Elle raccroche le manteau.
-papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau bleu.
+narrateur|Elle boutonne jusqu'en haut.
+maman|Le ballon rouge, Sarah.
+enfant-f|Le ballon.
+narrateur|Un chat passe près du pas de porte.
+narrateur|Sarah sort, manteau boutonné.
+narrateur|Le ballon roule vers le banc.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+papa|Bravo.
+papa|Les boutons sont encore fermés, puis elle les ouvre.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7311,7 +7583,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7479,7 +7751,7 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -7511,7 +7783,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi bleu. Puis le ballon rouge. Puis le chat. Un vélo passe au loin. Nora sourit. Papa sourit aussi. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat suit le ballon des yeux. Un vélo passe au loin. On reste dans le jardin. Le chat a vu le ballon. Sarah a le manteau bleu, tout boutonné. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah sourit au chat, derrière la vitre. Il reste dehors.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7651,7 +7923,18 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi bleu. Puis le ballon rouge. Puis le chat. Un vélo passe au loin. Nora sourit. Papa sourit aussi. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chat suit le ballon des yeux.
+narrateur|Un vélo passe au loin.
+maman|On reste dans le jardin.
+enfant-f|Le chat a vu le ballon.
+narrateur|Sarah a le manteau bleu, tout boutonné.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+papa|Bravo.
+narrateur|Sarah sourit au chat, derrière la vitre.
+maman|Il reste dehors.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7679,7 +7962,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon s'immobilise dans l'entrée. Bravo, Sarah. Tu as raccroché. Merci. Les boutons du manteau bleu sont ouverts, maintenant. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7819,7 +8102,13 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le ballon s'immobilise dans l'entrée.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Les boutons du manteau bleu sont ouverts, maintenant.
+papa|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7847,7 +8136,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nora s'arrête près de le chien. le ballon rouge est rangé. Un linge sèche à l'air. Nora s'assoit près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien remue derrière la barrière. Un linge sèche à l'air, sur le fil. On dit bonjour, de loin. Bonjour. Sarah tient le ballon contre le manteau bleu. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah s'assoit pour défaire un bouton. Tu y arrives.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7987,7 +8276,18 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. Un linge sèche à l'air. Nora s'assoit près de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien remue derrière la barrière.
+narrateur|Un linge sèche à l'air, sur le fil.
+papa|On dit bonjour, de loin.
+enfant-f|Bonjour.
+narrateur|Sarah tient le ballon contre le manteau bleu.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+maman|Bravo.
+narrateur|Sarah s'assoit pour défaire un bouton.
+papa|Tu y arrives.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -8019,7 +8319,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le linge claque un peu, dehors. Bravo, Sarah. Tu as raccroché. Merci, maman. Le manteau bleu pend, lourd et chaud. On a bien sorti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8159,7 +8459,13 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le linge claque un peu, dehors.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci, maman.
+narrateur|Le manteau bleu pend, lourd et chaud.
+maman|On a bien sorti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8187,7 +8493,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Nora se souvient de bleu. Et de le ballon rouge. Et de la poule. On entend un oiseau. Nora écoute papa encore une fois. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule picore près du compost. On entend un oiseau, plus haut. On écoute les deux. La poule, et l'oiseau. Sarah a le manteau bleu. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah pose le ballon sous le banc de l'entrée. Bien.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8327,7 +8633,18 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Nora se souvient de bleu. Et de le ballon rouge. Et de la poule. On entend un oiseau. Nora écoute papa encore une fois. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|La poule picore près du compost.
+narrateur|On entend un oiseau, plus haut.
+maman|On écoute les deux.
+enfant-f|La poule, et l'oiseau.
+narrateur|Sarah a le manteau bleu.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+papa|Bravo.
+narrateur|Sarah pose le ballon sous le banc de l'entrée.
+maman|Bien.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8355,7 +8672,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah boit une gorgée d'eau. Bravo, Sarah. Tu as fait du bon travail. Merci. Le manteau bleu est au crochet. Avant de sortir, on prend son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8495,7 +8812,13 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah boit une gorgée d'eau.
+papa|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le manteau bleu est au crochet.
+papa|Avant de sortir, on prend son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8523,7 +8846,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le seau bleu, manteau boutonné. Un chat miaule. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau bleu. Les boutons font un petit bruit. Le seau bleu, Sarah. Le seau. Un chat miaule une fois, tout doux. Sarah sort. Elle puise des feuilles dans le seau. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Le seau sent l'herbe.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8663,7 +8986,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le seau bleu, manteau boutonné. Un chat miaule. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau bleu.
+narrateur|Les boutons font un petit bruit.
+papa|Le seau bleu, Sarah.
+enfant-f|Le seau.
+narrateur|Un chat miaule une fois, tout doux.
+narrateur|Sarah sort.
+narrateur|Elle puise des feuilles dans le seau.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+maman|Bravo.
+maman|Le seau sent l'herbe.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8691,7 +9026,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8859,7 +9194,7 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -8891,7 +9226,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après le seau bleu. Près de bleu. Nora s'arrête. Un chat miaule une fois. J'ai appris. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat miaule une fois, près du seau. Sarah s'arrête. On le laisse passer. Il est passé. Sarah a le manteau bleu, et le seau. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Les feuilles du seau sentent encore l'herbe. On les verse au jardin, demain.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9031,9 +9366,18 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après le seau bleu. Près de bleu. Nora s'arrête. Un chat miaule une fois.
-enfant-f|J'ai appris. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau.
-narrateur|Nora dit merci à papa.</t>
+          <t>narrateur|Le chat miaule une fois, près du seau.
+narrateur|Sarah s'arrête.
+papa|On le laisse passer.
+enfant-f|Il est passé.
+narrateur|Sarah a le manteau bleu, et le seau.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+maman|Bravo.
+narrateur|Les feuilles du seau sentent encore l'herbe.
+papa|On les verse au jardin, demain.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9061,7 +9405,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah pose le seau près du paillasson. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau bleu est à sa place. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9201,7 +9545,13 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah pose le seau près du paillasson.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci, papa.
+narrateur|Le manteau bleu est à sa place.
+maman|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9229,7 +9579,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Nora range le seau bleu. le chien reste près de bleu. Le sol est un peu froid. Nora ferme la porte, tout doux. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien reste près du bleu du manteau, derrière le grillage. Le sol de l'entrée est un peu froid. On rentre maintenant. D'accord. Tu as pris ton manteau pour sortir. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah ferme un à un les boutons, à l'envers, pour les ouvrir. Tu y vas doucement. Oui.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9369,7 +9719,18 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Nora range le seau bleu. le chien reste près de bleu. Le sol est un peu froid. Nora ferme la porte, tout doux. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien reste près du bleu du manteau, derrière le grillage.
+narrateur|Le sol de l'entrée est un peu froid.
+maman|On rentre maintenant.
+enfant-f|D'accord.
+papa|Tu as pris ton manteau pour sortir.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+papa|Bravo.
+narrateur|Sarah ferme un à un les boutons, à l'envers, pour les ouvrir.
+maman|Tu y vas doucement.
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9401,7 +9762,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah pose les pieds sur le tapis de l'entrée. Bravo, Sarah. Tu as raccroché. Merci. Le seau bleu reste près des chaussures. On a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9541,7 +9902,13 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah pose les pieds sur le tapis de l'entrée.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Le seau bleu reste près des chaussures.
+papa|On a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9569,7 +9936,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. le seau bleu aussi. bleu reste dans le souvenir. La lumière est claire. Nora raccroche un linge. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule est là, près du compost. Le seau bleu aussi, dans les mains de Sarah. On la regarde. Elle picore. La lumière est claire sur le manteau bleu. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah pose le seau, puis ses mains. Bien.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9709,7 +10076,18 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. le seau bleu aussi. bleu reste dans le souvenir. La lumière est claire. Nora raccroche un linge. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|La poule est là, près du compost.
+narrateur|Le seau bleu aussi, dans les mains de Sarah.
+papa|On la regarde.
+enfant-f|Elle picore.
+narrateur|La lumière est claire sur le manteau bleu.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+maman|Bravo.
+narrateur|Sarah pose le seau, puis ses mains.
+papa|Bien.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9737,7 +10115,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah souffle sur ses doigts, un peu froids. Bravo, Sarah. Tu as fait du bon travail. Merci, maman. Le manteau bleu sèche au crochet. Avant de sortir, on prend son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9877,7 +10255,13 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah souffle sur ses doigts, un peu froids.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le manteau bleu sèche au crochet.
+maman|Avant de sortir, on prend son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9905,7 +10289,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le doudou, manteau boutonné. Un chat se frotte. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau bleu. Elle boutonne le dernier bouton. Le doudou, Sarah. Le doudou. Un chat se frotte contre la jambe de papa. Sarah sort, le doudou sous le bras. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Le doudou a une odeur de maison.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -10045,7 +10429,18 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le doudou, manteau boutonné. Un chat se frotte. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau bleu.
+narrateur|Elle boutonne le dernier bouton.
+maman|Le doudou, Sarah.
+enfant-f|Le doudou.
+narrateur|Un chat se frotte contre la jambe de papa.
+narrateur|Sarah sort, le doudou sous le bras.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+papa|Bravo.
+papa|Le doudou a une odeur de maison.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10073,7 +10468,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10241,7 +10636,7 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -10273,7 +10668,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint le chat. le doudou est rangé. bleu est fini. On écoute jusqu'au bout. Nora range la tasse. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat rejoint Sarah près du doudou. On écoute jusqu'au bout son petit ronron. Il est content. Moi aussi. Sarah a le manteau bleu. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah range le doudou sur la chaise. Merci.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10413,7 +10808,18 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint le chat. le doudou est rangé. bleu est fini. On écoute jusqu'au bout. Nora range la tasse. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chat rejoint Sarah près du doudou.
+narrateur|On écoute jusqu'au bout son petit ronron.
+maman|Il est content.
+enfant-f|Moi aussi.
+narrateur|Sarah a le manteau bleu.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+papa|Bravo.
+narrateur|Sarah range le doudou sur la chaise.
+maman|Merci.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10441,7 +10847,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'assoit pour ouvrir les boutons. Bravo, Sarah. Tu as raccroché. Merci. Le manteau bleu pend, vide et chaud. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10581,7 +10987,13 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah s'assoit pour ouvrir les boutons.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Le manteau bleu pend, vide et chaud.
+papa|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10609,7 +11021,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Nora pose le doudou. bleu est derrière. Le vent est doux. Nora caresse le doudou. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien s'assoit de l'autre côté de la barrière. Le vent est doux dans le capuchon vide. On caresse le doudou, pas le chien. Le doudou est à moi. Sarah a le manteau bleu. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah caresse le doudou sur ses genoux. Bien.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10749,7 +11161,18 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Nora pose le doudou. bleu est derrière. Le vent est doux. Nora caresse le doudou. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien s'assoit de l'autre côté de la barrière.
+narrateur|Le vent est doux dans le capuchon vide.
+papa|On caresse le doudou, pas le chien.
+enfant-f|Le doudou est à moi.
+narrateur|Sarah a le manteau bleu.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+maman|Bravo.
+narrateur|Sarah caresse le doudou sur ses genoux.
+papa|Bien.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -10781,7 +11204,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les chaussures font toc toc, puis s'arrêtent. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau bleu est au crochet. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10921,7 +11344,13 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les chaussures font toc toc, puis s'arrêtent.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci, papa.
+narrateur|Le manteau bleu est au crochet.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10949,7 +11378,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Nora montre la poule. Papa a vu bleu. Et le doudou. Les chaussures font toc toc. Nora dit merci à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Sarah montre la poule à papa. J'ai vu le manteau bleu. Et le doudou. Les chaussures font toc toc sur le chemin. On rentre ? Oui. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Merci. Tu as pris ton manteau pour sortir.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11089,7 +11518,18 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Nora montre la poule. Papa a vu bleu. Et le doudou. Les chaussures font toc toc. Nora dit merci à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Sarah montre la poule à papa.
+papa|J'ai vu le manteau bleu.
+papa|Et le doudou.
+maman|Les chaussures font toc toc sur le chemin.
+enfant-f|On rentre ?
+maman|Oui.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau bleu.
+maman|Bravo.
+enfant-f|Merci.
+papa|Tu as pris ton manteau pour sortir.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11117,7 +11557,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah dit merci encore une fois. Bravo, Sarah. Tu as fait du bon travail. Le doudou est sur la chaise. Le manteau bleu attend au crochet. Avant de sortir, on prend son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11257,7 +11697,13 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah dit merci encore une fois.
+papa|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+enfant-f|Le doudou est sur la chaise.
+narrateur|Le manteau bleu attend au crochet.
+papa|Avant de sortir, on prend son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11285,7 +11731,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Nora prend son manteau vert. Elle enfile les manches. Elle sort. Une feuille colle au tissu. Puis elle rentre. Elle raccroche le manteau. Maman l'aide à trouver le crochet.</t>
+          <t>Sarah prend le manteau vert. Le capuchon est doux à l'intérieur. Une feuille sèche colle encore au tissu. On enlève la feuille. Sarah l'enlève d'un doigt. Elle glisse les manches, puis le capuchon. Bravo. Tu as pris ton manteau avant de sortir. Sarah sort. L'air sent les feuilles mouillées. Puis elle rentre. Le crochet, Sarah. Sarah raccroche le manteau vert. Tu as raccroché. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11425,7 +11871,21 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Nora prend son manteau vert. Elle enfile les manches. Elle sort. Une feuille colle au tissu. Puis elle rentre. Elle raccroche le manteau. Maman l'aide à trouver le crochet.</t>
+          <t>narrateur|Sarah prend le manteau vert.
+narrateur|Le capuchon est doux à l'intérieur.
+narrateur|Une feuille sèche colle encore au tissu.
+maman|On enlève la feuille.
+narrateur|Sarah l'enlève d'un doigt.
+narrateur|Elle glisse les manches, puis le capuchon.
+papa|Bravo.
+papa|Tu as pris ton manteau avant de sortir.
+narrateur|Sarah sort.
+narrateur|L'air sent les feuilles mouillées.
+narrateur|Puis elle rentre.
+maman|Le crochet, Sarah.
+narrateur|Sarah raccroche le manteau vert.
+papa|Tu as raccroché.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11641,7 +12101,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On prend son manteau avant de sortir. Nora hoche la tête. On continue, avec papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Oui. On prend son manteau avant de sortir. Quand on rentre, on le raccroche. Bravo, Sarah. Tu as enlevé la feuille. Le manteau vert est à sa place. Le crochet est à ma hauteur. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11785,7 +12245,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On prend son manteau avant de sortir. Nora hoche la tête. On continue, avec papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Oui.
+narrateur|On prend son manteau avant de sortir.
+narrateur|Quand on rentre, on le raccroche.
+maman|Bravo, Sarah.
+maman|Tu as enlevé la feuille.
+papa|Le manteau vert est à sa place.
+enfant-f|Le crochet est à ma hauteur.
+maman|On continue ensemble ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -12009,7 +12477,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le ballon. Un chien marche au loin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau vert. Elle met le capuchon. Le ballon, Sarah. Le ballon. Un chien marche au loin, sur le chemin. Sarah sort. Le ballon rebondit près des feuilles. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Le capuchon retombe dans le dos, au crochet.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12149,7 +12617,19 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le ballon. Un chien marche au loin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa reste tout près. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau vert.
+narrateur|Elle met le capuchon.
+papa|Le ballon, Sarah.
+enfant-f|Le ballon.
+narrateur|Un chien marche au loin, sur le chemin.
+narrateur|Sarah sort.
+narrateur|Le ballon rebondit près des feuilles.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+maman|Bravo.
+maman|Le capuchon retombe dans le dos, au crochet.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -12181,7 +12661,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12349,7 +12829,7 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -12381,7 +12861,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi vert. Puis le ballon rouge. Puis le chat. Une pomme brille un peu. Nora boit une gorgée d'eau. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat s'assoit près du ballon, sous le capuchon d'ombre. Une pomme du voisin brille un peu, dans l'herbe. La pomme reste au jardin du voisin. Le chat, lui, est là. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah boit une gorgée, puis pose le ballon. Bien.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12521,7 +13001,18 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi vert. Puis le ballon rouge. Puis le chat. Une pomme brille un peu. Nora boit une gorgée d'eau. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chat s'assoit près du ballon, sous le capuchon d'ombre.
+narrateur|Une pomme du voisin brille un peu, dans l'herbe.
+maman|La pomme reste au jardin du voisin.
+enfant-f|Le chat, lui, est là.
+narrateur|Sarah a le manteau vert.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+papa|Bravo.
+narrateur|Sarah boit une gorgée, puis pose le ballon.
+maman|Bien.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12549,7 +13040,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le capuchon du manteau vert retombe au crochet. Bravo, Sarah. Tu as raccroché. Merci. Le ballon reste sous le banc. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12689,7 +13180,13 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le capuchon du manteau vert retombe au crochet.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Le ballon reste sous le banc.
+papa|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12717,7 +13214,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Nora s'arrête près de le chien. le ballon rouge est rangé. On dit merci. Maman n'est pas loin. Nora les rejoint. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien s'arrête près de la barrière. On dit merci au vent, tout bas. On reste de notre côté. D'accord. Maman n'est pas loin, près du store. Tu as pris ton manteau. Sarah rentre, le ballon sous le bras. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah s'essuie les mains. Bien.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12857,7 +13354,18 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Nora s'arrête près de le chien. le ballon rouge est rangé. On dit merci. Maman n'est pas loin. Nora les rejoint. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien s'arrête près de la barrière.
+narrateur|On dit merci au vent, tout bas.
+papa|On reste de notre côté.
+enfant-f|D'accord.
+narrateur|Maman n'est pas loin, près du store.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre, le ballon sous le bras.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+maman|Bravo.
+narrateur|Sarah s'essuie les mains.
+papa|Bien.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -12889,7 +13397,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah pose le ballon, puis ses mains sur le radiateur. Bravo, Sarah. Tu as raccroché. Merci, maman. Le manteau vert sèche au crochet. On a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -13029,7 +13537,13 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah pose le ballon, puis ses mains sur le radiateur.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci, maman.
+narrateur|Le manteau vert sèche au crochet.
+maman|On a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -13057,7 +13571,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Nora se souvient de vert. Et de le ballon rouge. Et de la poule. Un panier est posé sur le banc. Nora serre la main de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule picore près d'un panier, chez le voisin. Le panier est posé sur le muret. On la regarde. Elle est drôle. Sarah a le manteau vert, et le ballon. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah pose le ballon près du panier de l'entrée. Notre panier, à nous.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13197,7 +13711,18 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Nora se souvient de vert. Et de le ballon rouge. Et de la poule. Un panier est posé sur le banc. Nora serre la main de papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|La poule picore près d'un panier, chez le voisin.
+narrateur|Le panier est posé sur le muret.
+papa|On la regarde.
+enfant-f|Elle est drôle.
+narrateur|Sarah a le manteau vert, et le ballon.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+maman|Bravo.
+narrateur|Sarah pose le ballon près du panier de l'entrée.
+papa|Notre panier, à nous.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13225,7 +13750,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'assoit pour enlever le capuchon, déjà raccroché. Bravo, Sarah. Tu as fait du bon travail. Merci. Le manteau vert est à sa place. Avant de sortir, on prend son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13365,7 +13890,13 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah s'assoit pour enlever le capuchon, déjà raccroché.
+papa|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le manteau vert est à sa place.
+papa|Avant de sortir, on prend son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13393,7 +13924,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le seau. Un chien marche au loin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau vert. Elle glisse les manches. Le seau, Sarah. Le seau. Un chien marche au loin. Sarah sort. Elle ramasse des cailloux lisses dans le seau. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Les cailloux restent dans le seau.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13533,7 +14064,19 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le seau. Un chien marche au loin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Papa montre le geste, lentement. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau vert.
+narrateur|Elle glisse les manches.
+maman|Le seau, Sarah.
+enfant-f|Le seau.
+narrateur|Un chien marche au loin.
+narrateur|Sarah sort.
+narrateur|Elle ramasse des cailloux lisses dans le seau.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+papa|Bravo.
+papa|Les cailloux restent dans le seau.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -13565,7 +14108,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13733,7 +14276,7 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -13765,7 +14308,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après le seau bleu. Près de vert. Nora s'arrête. Une feuille tombe. Nora plie un pull. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat suit le seau des yeux. Une feuille tombe dans l'eau du seau. On la laisse. Elle flotte. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah plie le capuchon sur le crochet. Bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13905,7 +14448,18 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après le seau bleu. Près de vert. Nora s'arrête. Une feuille tombe. Nora plie un pull. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chat suit le seau des yeux.
+narrateur|Une feuille tombe dans l'eau du seau.
+maman|On la laisse.
+enfant-f|Elle flotte.
+narrateur|Sarah a le manteau vert.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+papa|Bravo.
+narrateur|Sarah plie le capuchon sur le crochet.
+maman|Bien.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13933,7 +14487,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah pose le seau, tout droit. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau vert pend, avec son capuchon. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14073,7 +14627,13 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah pose le seau, tout droit.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci, papa.
+narrateur|Le manteau vert pend, avec son capuchon.
+maman|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14101,7 +14661,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Nora range le seau bleu. le chien reste près de vert. Le savon sent bon. Nora pose le seau bleu à sa place. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien reste près du manteau vert, derrière le grillage. Le savon de l'entrée sent bon. On se lave les mains, après le seau. D'accord. Tu as pris ton manteau pour sortir. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah pose le seau, puis se lave les mains. C'est du bon travail. Ça sent le savon.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14241,7 +14801,18 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Nora range le seau bleu. le chien reste près de vert. Le savon sent bon. Nora pose le seau bleu à sa place. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien reste près du manteau vert, derrière le grillage.
+narrateur|Le savon de l'entrée sent bon.
+papa|On se lave les mains, après le seau.
+enfant-f|D'accord.
+maman|Tu as pris ton manteau pour sortir.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+maman|Bravo.
+narrateur|Sarah pose le seau, puis se lave les mains.
+papa|C'est du bon travail.
+enfant-f|Ça sent le savon.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -14273,7 +14844,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les mains de Sarah sont propres et un peu froides. Bravo, Sarah. Tu as raccroché. Merci. Le manteau vert est au crochet. On a bien sorti. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14413,7 +14984,13 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les mains de Sarah sont propres et un peu froides.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Le manteau vert est au crochet.
+papa|On a bien sorti.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14441,7 +15018,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. le seau bleu aussi. vert reste dans le souvenir. On range un objet. Nora montre la poule à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>La poule est là, près du seau bleu, de l'autre côté. Sarah range un caillou dans sa tête, comme un souvenir. Le caillou reste dans le seau. Oui. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah pose le seau près du savon. Bien.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14581,7 +15158,18 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. le seau bleu aussi. vert reste dans le souvenir. On range un objet. Nora montre la poule à papa. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|La poule est là, près du seau bleu, de l'autre côté.
+narrateur|Sarah range un caillou dans sa tête, comme un souvenir.
+maman|Le caillou reste dans le seau.
+enfant-f|Oui.
+narrateur|Sarah a le manteau vert.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+papa|Bravo.
+narrateur|Sarah pose le seau près du savon.
+maman|Bien.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14609,7 +15197,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'essuie les mains sur le linge. Bravo, Sarah. Tu as fait du bon travail. Merci, maman. Le manteau vert attend au crochet. Avant de sortir, on prend son manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14749,7 +15337,13 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah s'essuie les mains sur le linge.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|Merci, maman.
+narrateur|Le manteau vert attend au crochet.
+maman|Avant de sortir, on prend son manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14777,7 +15371,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Nora sort avec le doudou. Une poule caquette chez le voisin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau. Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>Sarah reprend le manteau vert. Le capuchon est chaud autour des oreilles. Le doudou, Sarah. Le doudou. Une poule caquette chez le voisin. Sarah sort, le doudou contre la joue. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. La poule s'est tue.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14917,8 +15511,18 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Nora sort avec le doudou. Une poule caquette chez le voisin. Elle a pris son manteau. Puis elle rentre. Elle raccroche le manteau.
-papa|Je suis là. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche.</t>
+          <t>narrateur|Sarah reprend le manteau vert.
+narrateur|Le capuchon est chaud autour des oreilles.
+papa|Le doudou, Sarah.
+enfant-f|Le doudou.
+narrateur|Une poule caquette chez le voisin.
+narrateur|Sarah sort, le doudou contre la joue.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+maman|Bravo.
+maman|La poule s'est tue.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14946,7 +15550,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15114,7 +15718,7 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|On peut aller vers le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -15146,7 +15750,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint le chat. le doudou est rangé. vert est fini. On souffle doucement. Nora tend le chat à maman. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chat rejoint le doudou, tout contre la jambe. On souffle doucement. On est calmes. Le chat est calme. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah tend le doudou à maman, puis le reprend. Il reste avec toi.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15286,7 +15890,18 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint le chat. le doudou est rangé. vert est fini. On souffle doucement. Nora tend le chat à maman. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chat rejoint le doudou, tout contre la jambe.
+narrateur|On souffle doucement.
+papa|On est calmes.
+enfant-f|Le chat est calme.
+narrateur|Sarah a le manteau vert.
+maman|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+papa|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+maman|Bravo.
+narrateur|Sarah tend le doudou à maman, puis le reprend.
+papa|Il reste avec toi.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15314,7 +15929,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'assoit, le doudou sur les genoux. Bravo, Sarah. Tu as raccroché. Merci. Le manteau vert est à sa place. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15454,7 +16069,13 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah s'assoit, le doudou sur les genoux.
+papa|Bravo, Sarah.
+maman|Tu as raccroché.
+enfant-f|Merci.
+narrateur|Le manteau vert est à sa place.
+papa|Quand on rentre, on raccroche le manteau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15482,7 +16103,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Nora pose le doudou. vert est derrière. Un galet est encore chaud. Nora répète tout bas le geste. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Le chien s'assoit, de l'autre côté. Un galet est encore chaud, près du pas de porte. On laisse le galet. Le doudou, je le garde. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah pose le doudou, puis le reprend. Bien.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15622,7 +16243,18 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Nora pose le doudou. vert est derrière. Un galet est encore chaud. Nora répète tout bas le geste. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Le chien s'assoit, de l'autre côté.
+narrateur|Un galet est encore chaud, près du pas de porte.
+maman|On laisse le galet.
+enfant-f|Le doudou, je le garde.
+narrateur|Sarah a le manteau vert.
+papa|Tu as pris ton manteau.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+papa|Bravo.
+narrateur|Sarah pose le doudou, puis le reprend.
+maman|Bien.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -15654,7 +16286,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah souffle sur le galet, par la vitre. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau vert pend au crochet. On a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15794,7 +16426,13 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah souffle sur le galet, par la vitre.
+maman|Bravo, Sarah.
+papa|Tu as raccroché.
+enfant-f|Merci, papa.
+narrateur|Le manteau vert pend au crochet.
+maman|On a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15822,7 +16460,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Nora montre la poule. Papa a vu vert. Et le doudou. Il y a des miettes sur la table. Nora essuie ses mains. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>Sarah montre la poule. J'ai vu le manteau vert. Et le doudou. Il y a des miettes sur la table de l'entrée. On les essuie après. On rentre ? Oui. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Tu as pris ton manteau pour sortir.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15962,7 +16600,18 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Nora montre la poule. Papa a vu vert. Et le doudou. Il y a des miettes sur la table. Nora essuie ses mains. Avant de sortir, prendre son manteau. Quand on rentre, on le raccroche. On prend son manteau. Prendre son manteau, puis sortir. Quand on rentre, on raccroche le manteau. Nora dit merci à papa.</t>
+          <t>narrateur|Sarah montre la poule.
+papa|J'ai vu le manteau vert.
+papa|Et le doudou.
+narrateur|Il y a des miettes sur la table de l'entrée.
+maman|On les essuie après.
+enfant-f|On rentre ?
+papa|Oui.
+narrateur|Sarah rentre.
+maman|On raccroche le manteau.
+narrateur|Sarah raccroche le manteau vert.
+papa|Bravo.
+maman|Tu as pris ton manteau pour sortir.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15990,7 +16639,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah essuie une miette d'un doigt. Bravo, Sarah. Tu as fait du bon travail. Merci. Le doudou est sur la chaise. Le manteau vert est au crochet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16130,7 +16779,13 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah essuie une miette d'un doigt.
+papa|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le doudou est sur la chaise.
+papa|Le manteau vert est au crochet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16152,7 +16807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16190,6 +16845,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-002.xlsx
+++ b/stories/arbres/TREE-AUT-002.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de l'entrée est toute embuée. Sarah y dessine un petit rond du doigt. Dehors, le jardin est gris et frais. Les feuilles collent au banc de bois. Un crochet de manteau attend près de la porte. Le crochet est bas, à hauteur d'enfant. Ça sent la terre mouillée, tout doux. L'horloge de la cuisine fait tic tac. Papa lace une chaussure, puis l'autre. Les chaussures sont prêtes, Sarah. Maman soulève un peu le store. Tu as vu le banc, tout mouillé ? Oui, maman. Trois manteaux pendent, rouge, bleu, vert. Je veux sortir ! Je veux jouer dehors. D'accord. Avant de sortir, on prend son manteau. Quand on rentre, on le raccroche. Sarah touche le tissu le plus proche. En ce moment, elle a trop envie de courir au jardin.</t>
+          <t>La vitre de l'entrée est toute embuée. Sarah y dessine un petit rond du doigt. Dehors, le jardin est gris et frais. Les feuilles collent au banc de bois. Un crochet de manteau attend près de la porte. Le crochet est bas, à hauteur d'enfant. Ça sent la terre mouillée, tout doux. L'horloge de la cuisine fait tic tac. Papa lace une chaussure, puis l'autre. Les chaussures sont prêtes, Sarah. Maman soulève un peu le store. Tu as vu le banc, tout mouillé ? Oui, maman. Trois manteaux pendent, rouge, bleu, vert. Je veux sortir ! Je veux jouer dehors. D'accord. Avant de sortir, on prend son manteau. Quand c'est l'heure de rentrer, on le raccroche. Sarah touche le tissu le plus proche. En ce moment, elle a trop envie de courir au jardin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
 enfant-f|Je veux jouer dehors.
 papa|D'accord.
 papa|Avant de sortir, on prend son manteau.
-maman|Quand on rentre, on le raccroche.
+maman|Quand c'est l'heure de rentrer, on le raccroche.
 narrateur|Sarah touche le tissu le plus proche.
 narrateur|En ce moment, elle a trop envie de courir au jardin.</t>
         </is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On prend son manteau avant de sortir. Quand on rentre, on le raccroche. Bravo, Sarah. Tu as écouté. Le manteau rouge est à sa place. Je peux ressortir ? Oui. On reprend le manteau, puis on sort. D'accord.</t>
+          <t>Oui. On prend son manteau avant de sortir. Quand c'est l'heure de rentrer, on le raccroche. Bravo, Sarah. Tu as écouté. Le manteau rouge est à sa place. Je peux ressortir ? Oui. On reprend le manteau, puis on sort. D'accord.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
         <is>
           <t>narrateur|Oui.
 narrateur|On prend son manteau avant de sortir.
-narrateur|Quand on rentre, on le raccroche.
+narrateur|Quand c'est l'heure de rentrer, on le raccroche.
 maman|Bravo, Sarah.
 maman|Tu as écouté.
 papa|Le manteau rouge est à sa place.
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Sarah souffle, puis sourit à papa. Bravo, Sarah. Tu as raccroché. Merci, maman. Le manteau rouge sèche un peu, au crochet. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Sarah souffle. Merci, papa. Bravo, Sarah. Tu as raccroché. Merci, maman. Le manteau rouge sèche un peu, au crochet. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3384,12 +3384,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|Sarah souffle, puis sourit à papa.
+          <t>narrateur|Sarah souffle.
+enfant-f|Merci, papa.
 papa|Bravo, Sarah.
 maman|Tu as raccroché.
 enfant-f|Merci, maman.
 narrateur|Le manteau rouge sèche un peu, au crochet.
-papa|Quand on rentre, on raccroche le manteau.
+papa|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -3418,7 +3419,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>La poule du voisin picore près du grillage. Elle fait un petit bruit. On la regarde, sans courir. La poule. Le ballon reste sous le bras de Sarah. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. L'eau de la gouttière coule, tout petit bruit. La poule reste chez le voisin.</t>
+          <t>La poule du voisin picore près du grillage. Elle fait un petit bruit. On la regarde, tout doux. La poule. Le ballon reste sous le bras de Sarah. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. L'eau de la gouttière coule, tout petit bruit. La poule reste chez le voisin.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3560,7 +3561,7 @@
         <is>
           <t>narrateur|La poule du voisin picore près du grillage.
 narrateur|Elle fait un petit bruit.
-maman|On la regarde, sans courir.
+maman|On la regarde, tout doux.
 enfant-f|La poule.
 narrateur|Le ballon reste sous le bras de Sarah.
 papa|Tu as pris ton manteau.
@@ -3771,7 +3772,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sarah reprend le manteau rouge. Elle glisse les manches. Le seau bleu, Sarah. Le seau. Le seau est léger, la anse est lisse. Sarah sort. Elle ramasse des feuilles mouillées. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Le seau reste près des chaussures.</t>
+          <t>Sarah reprend le manteau rouge. Elle glisse les manches. Le seau bleu, Sarah. Le seau. Le seau est léger, l'anse est lisse. Sarah sort. Elle ramasse des feuilles mouillées. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau rouge. Bravo. Le seau reste près des chaussures.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3915,7 +3916,7 @@
 narrateur|Elle glisse les manches.
 maman|Le seau bleu, Sarah.
 enfant-f|Le seau.
-narrateur|Le seau est léger, la anse est lisse.
+narrateur|Le seau est léger, l'anse est lisse.
 narrateur|Sarah sort.
 narrateur|Elle ramasse des feuilles mouillées.
 papa|Tu as pris ton manteau.
@@ -4330,7 +4331,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Sarah range le rouge dans sa tête, comme un souvenir. Bravo, Sarah. Tu as raccroché. Merci, papa. Le seau bleu reste près de la porte. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Sarah range le rouge dans sa tête, comme un souvenir. Bravo, Sarah. Tu as raccroché. Merci, papa. Le seau bleu reste près de la porte. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4475,7 +4476,7 @@
 papa|Tu as raccroché.
 enfant-f|Merci, papa.
 narrateur|Le seau bleu reste près de la porte.
-maman|Quand on rentre, on raccroche le manteau.
+maman|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -5773,7 +5774,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Sarah range le doudou sur la chaise. Bravo, Sarah. Tu as raccroché. Merci. Le manteau rouge attend au crochet. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Sarah range le doudou sur la chaise. Bravo, Sarah. Tu as raccroché. Merci. Le manteau rouge attend au crochet. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5918,7 +5919,7 @@
 maman|Tu as raccroché.
 enfant-f|Merci.
 narrateur|Le manteau rouge attend au crochet.
-papa|Quand on rentre, on raccroche le manteau.
+papa|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -7027,7 +7028,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On prend son manteau. Avant de sortir, on prend son manteau. Bravo, Sarah. Tu as boutonné jusqu'en haut. Quand on rentre, on raccroche le manteau. Il est au crochet. On continue ensemble ? Oui.</t>
+          <t>Oui. On prend son manteau. Avant de sortir, on prend son manteau. Bravo, Sarah. Tu as boutonné jusqu'en haut. Quand c'est l'heure de rentrer, on raccroche le manteau. Il est au crochet. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -7176,7 +7177,7 @@
 narrateur|Avant de sortir, on prend son manteau.
 papa|Bravo, Sarah.
 papa|Tu as boutonné jusqu'en haut.
-maman|Quand on rentre, on raccroche le manteau.
+maman|Quand c'est l'heure de rentrer, on raccroche le manteau.
 enfant-f|Il est au crochet.
 papa|On continue ensemble ?
 enfant-f|Oui.</t>
@@ -7783,7 +7784,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Le chat suit le ballon des yeux. Un vélo passe au loin. On reste dans le jardin. Le chat a vu le ballon. Sarah a le manteau bleu, tout boutonné. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah sourit au chat, derrière la vitre. Il reste dehors.</t>
+          <t>Le chat suit le ballon des yeux. Un vélo passe au loin. On reste dans le jardin. Le chat a vu le ballon. Sarah a le manteau bleu, tout boutonné. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah fait coucou au chat, derrière la vitre. Il reste dehors.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7933,7 +7934,7 @@
 maman|On raccroche le manteau.
 narrateur|Sarah raccroche le manteau bleu.
 papa|Bravo.
-narrateur|Sarah sourit au chat, derrière la vitre.
+narrateur|Sarah fait coucou au chat, derrière la vitre.
 maman|Il reste dehors.</t>
         </is>
       </c>
@@ -7962,7 +7963,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Le ballon s'immobilise dans l'entrée. Bravo, Sarah. Tu as raccroché. Merci. Les boutons du manteau bleu sont ouverts, maintenant. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Le ballon s'immobilise dans l'entrée. Bravo, Sarah. Tu as raccroché. Merci. Les boutons du manteau bleu sont ouverts, maintenant. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -8107,7 +8108,7 @@
 maman|Tu as raccroché.
 enfant-f|Merci.
 narrateur|Les boutons du manteau bleu sont ouverts, maintenant.
-papa|Quand on rentre, on raccroche le manteau.
+papa|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -9405,7 +9406,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le seau près du paillasson. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau bleu est à sa place. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Sarah pose le seau près du paillasson. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau bleu est à sa place. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9550,7 +9551,7 @@
 papa|Tu as raccroché.
 enfant-f|Merci, papa.
 narrateur|Le manteau bleu est à sa place.
-maman|Quand on rentre, on raccroche le manteau.
+maman|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -9936,7 +9937,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>La poule est là, près du compost. Le seau bleu aussi, dans les mains de Sarah. On la regarde. Elle picore. La lumière est claire sur le manteau bleu. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah pose le seau, puis ses mains. Bien.</t>
+          <t>La poule picore, près du compost. Le seau bleu aussi, dans les mains de Sarah. On la regarde. Elle picore. La lumière est claire sur le manteau bleu. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau bleu. Bravo. Sarah pose le seau, puis ses mains. Bien.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -10076,7 +10077,7 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là, près du compost.
+          <t>narrateur|La poule picore, près du compost.
 narrateur|Le seau bleu aussi, dans les mains de Sarah.
 papa|On la regarde.
 enfant-f|Elle picore.
@@ -10847,7 +10848,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Sarah s'assoit pour ouvrir les boutons. Bravo, Sarah. Tu as raccroché. Merci. Le manteau bleu pend, vide et chaud. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Sarah s'assoit pour ouvrir les boutons. Bravo, Sarah. Tu as raccroché. Merci. Le manteau bleu pend, vide et chaud. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10992,7 +10993,7 @@
 maman|Tu as raccroché.
 enfant-f|Merci.
 narrateur|Le manteau bleu pend, vide et chaud.
-papa|Quand on rentre, on raccroche le manteau.
+papa|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -12101,7 +12102,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On prend son manteau avant de sortir. Quand on rentre, on le raccroche. Bravo, Sarah. Tu as enlevé la feuille. Le manteau vert est à sa place. Le crochet est à ma hauteur. On continue ensemble ? Oui.</t>
+          <t>Oui. On prend son manteau avant de sortir. Quand c'est l'heure de rentrer, on le raccroche. Bravo, Sarah. Tu as enlevé la feuille. Le manteau vert est à sa place. Le crochet est à ma hauteur. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -12247,7 +12248,7 @@
         <is>
           <t>narrateur|Oui.
 narrateur|On prend son manteau avant de sortir.
-narrateur|Quand on rentre, on le raccroche.
+narrateur|Quand c'est l'heure de rentrer, on le raccroche.
 maman|Bravo, Sarah.
 maman|Tu as enlevé la feuille.
 papa|Le manteau vert est à sa place.
@@ -12861,7 +12862,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Le chat s'assoit près du ballon, sous le capuchon d'ombre. Une pomme du voisin brille un peu, dans l'herbe. La pomme reste au jardin du voisin. Le chat, lui, est là. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah boit une gorgée, puis pose le ballon. Bien.</t>
+          <t>Le chat s'assoit près du ballon, sous le capuchon d'ombre. Une pomme du voisin brille un peu, dans l'herbe. La pomme reste au jardin du voisin. Le chat, lui, s'assoit. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah boit une gorgée, puis pose le ballon. Bien.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -13004,7 +13005,7 @@
           <t>narrateur|Le chat s'assoit près du ballon, sous le capuchon d'ombre.
 narrateur|Une pomme du voisin brille un peu, dans l'herbe.
 maman|La pomme reste au jardin du voisin.
-enfant-f|Le chat, lui, est là.
+enfant-f|Le chat, lui, s'assoit.
 narrateur|Sarah a le manteau vert.
 papa|Tu as pris ton manteau.
 narrateur|Sarah rentre.
@@ -13040,7 +13041,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Le capuchon du manteau vert retombe au crochet. Bravo, Sarah. Tu as raccroché. Merci. Le ballon reste sous le banc. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Le capuchon du manteau vert retombe au crochet. Bravo, Sarah. Tu as raccroché. Merci. Le ballon reste sous le banc. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -13185,7 +13186,7 @@
 maman|Tu as raccroché.
 enfant-f|Merci.
 narrateur|Le ballon reste sous le banc.
-papa|Quand on rentre, on raccroche le manteau.
+papa|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -13214,7 +13215,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Le chien s'arrête près de la barrière. On dit merci au vent, tout bas. On reste de notre côté. D'accord. Maman n'est pas loin, près du store. Tu as pris ton manteau. Sarah rentre, le ballon sous le bras. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah s'essuie les mains. Bien.</t>
+          <t>Le chien s'arrête près de la barrière. On dit merci au vent, tout bas. On reste de notre côté. D'accord. Maman relève un peu le store. Tu as pris ton manteau. Sarah rentre, le ballon sous le bras. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah s'essuie les mains. Bien.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -13358,7 +13359,7 @@
 narrateur|On dit merci au vent, tout bas.
 papa|On reste de notre côté.
 enfant-f|D'accord.
-narrateur|Maman n'est pas loin, près du store.
+narrateur|Maman relève un peu le store.
 maman|Tu as pris ton manteau.
 narrateur|Sarah rentre, le ballon sous le bras.
 papa|On raccroche le manteau.
@@ -14487,7 +14488,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le seau, tout droit. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau vert pend, avec son capuchon. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Sarah pose le seau, tout droit. Bravo, Sarah. Tu as raccroché. Merci, papa. Le manteau vert pend, avec son capuchon. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14632,7 +14633,7 @@
 papa|Tu as raccroché.
 enfant-f|Merci, papa.
 narrateur|Le manteau vert pend, avec son capuchon.
-maman|Quand on rentre, on raccroche le manteau.
+maman|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -15018,7 +15019,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>La poule est là, près du seau bleu, de l'autre côté. Sarah range un caillou dans sa tête, comme un souvenir. Le caillou reste dans le seau. Oui. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah pose le seau près du savon. Bien.</t>
+          <t>La poule picore, près du seau bleu, de l'autre côté. Sarah range un caillou dans sa tête, comme un souvenir. Le caillou reste dans le seau. Oui. Sarah a le manteau vert. Tu as pris ton manteau. Sarah rentre. On raccroche le manteau. Sarah raccroche le manteau vert. Bravo. Sarah pose le seau près du savon. Bien.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -15158,7 +15159,7 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là, près du seau bleu, de l'autre côté.
+          <t>narrateur|La poule picore, près du seau bleu, de l'autre côté.
 narrateur|Sarah range un caillou dans sa tête, comme un souvenir.
 maman|Le caillou reste dans le seau.
 enfant-f|Oui.
@@ -15929,7 +15930,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Sarah s'assoit, le doudou sur les genoux. Bravo, Sarah. Tu as raccroché. Merci. Le manteau vert est à sa place. Quand on rentre, on raccroche le manteau. L'histoire est finie.</t>
+          <t>Sarah s'assoit, le doudou sur les genoux. Bravo, Sarah. Tu as raccroché. Merci. Le manteau vert est à sa place. Quand c'est l'heure de rentrer, on raccroche le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -16074,7 +16075,7 @@
 maman|Tu as raccroché.
 enfant-f|Merci.
 narrateur|Le manteau vert est à sa place.
-papa|Quand on rentre, on raccroche le manteau.
+papa|Quand c'est l'heure de rentrer, on raccroche le manteau.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -16807,7 +16808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16850,6 +16851,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
